--- a/docs/downloads/04/tbl_raisons_non_scol_marovoay_ampijoroa.xlsx
+++ b/docs/downloads/04/tbl_raisons_non_scol_marovoay_ampijoroa.xlsx
@@ -423,12 +423,6 @@
           <t>Main-d'oeuvre exploitation</t>
         </is>
       </c>
-      <c r="C4">
-        <v>4</v>
-      </c>
-      <c r="D4">
-        <v>6.9</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -477,12 +471,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C7">
-        <v>2</v>
-      </c>
-      <c r="D7">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -513,12 +501,6 @@
           <t>Besoin revenu</t>
         </is>
       </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9">
-        <v>1.7</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -549,12 +531,6 @@
           <t>Handicap / maladie</t>
         </is>
       </c>
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>0.8</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -567,12 +543,6 @@
           <t>Main-d'oeuvre exploitation</t>
         </is>
       </c>
-      <c r="C12">
-        <v>4</v>
-      </c>
-      <c r="D12">
-        <v>3.3</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -620,12 +590,6 @@
         <is>
           <t>École trop éloignée</t>
         </is>
-      </c>
-      <c r="C15">
-        <v>1</v>
-      </c>
-      <c r="D15">
-        <v>0.8</v>
       </c>
     </row>
   </sheetData>
